--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,7 +250,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>pdlgc-system.LGCNom</t>
+    <t>pdlgc-system.lgcNom</t>
   </si>
   <si>
     <t>1</t>
@@ -263,13 +263,13 @@
     <t>Nom du logiciel</t>
   </si>
   <si>
-    <t>pdlgc-system.LGCVersion</t>
+    <t>pdlgc-system.lgcVersion</t>
   </si>
   <si>
     <t>Version du logiciel</t>
   </si>
   <si>
-    <t>pdlgc-system.LGCIdentifiant</t>
+    <t>pdlgc-system.lgcIdentifiant</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -581,8 +581,8 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="23.171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="23.171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.28125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.28125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -612,7 +612,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="22.28125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
